--- a/XLSX_DATA/RAW_DATA/IND_raw_data.xlsx
+++ b/XLSX_DATA/RAW_DATA/IND_raw_data.xlsx
@@ -449,12 +449,12 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>gini</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>log_gdp_pc</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>gini</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -504,10 +504,10 @@
       <c r="F2" t="n">
         <v>620.699954330379</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
         <v>6.430847799841997</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>28.5998094242024</v>
       </c>
@@ -545,10 +545,10 @@
       <c r="F3" t="n">
         <v>654.355928429641</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
         <v>6.483651436488936</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>27.9122703698412</v>
       </c>
@@ -586,10 +586,10 @@
       <c r="F4" t="n">
         <v>667.598423095039</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
         <v>6.50368682973432</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>27.8370307633106</v>
       </c>
@@ -625,10 +625,10 @@
       <c r="F5" t="n">
         <v>695.293709344799</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
         <v>6.544334359666948</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>27.3030378517565</v>
       </c>
@@ -666,10 +666,10 @@
       <c r="F6" t="n">
         <v>742.53920839445</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
         <v>6.610075675201123</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>26.5192933488596</v>
       </c>
@@ -707,10 +707,10 @@
       <c r="F7" t="n">
         <v>756.704109527449</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
         <v>6.628972304540029</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>27.3258283775917</v>
       </c>
@@ -748,10 +748,10 @@
       <c r="F8" t="n">
         <v>778.5073775283651</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
         <v>6.657378467823068</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>26.4877773440307</v>
       </c>
@@ -789,10 +789,10 @@
       <c r="F9" t="n">
         <v>793.615912906381</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
         <v>6.676599607314973</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
         <v>27.6606541607882</v>
       </c>
@@ -830,10 +830,10 @@
       <c r="F10" t="n">
         <v>841.278894571674</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
         <v>6.734923227556812</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
         <v>27.4741071211988</v>
       </c>
@@ -872,10 +872,10 @@
         <v>892.596614581612</v>
       </c>
       <c r="G11" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="H11" t="n">
         <v>6.794134759427068</v>
-      </c>
-      <c r="H11" t="n">
-        <v>27.7</v>
       </c>
       <c r="I11" t="n">
         <v>29.219106305293</v>
@@ -914,10 +914,10 @@
       <c r="F12" t="n">
         <v>947.732565646672</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
         <v>6.854072358708038</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
         <v>29.5337641914637</v>
       </c>
@@ -955,10 +955,10 @@
       <c r="F13" t="n">
         <v>1008.23275343783</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
         <v>6.915954328164906</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
         <v>30.9272399435883</v>
       </c>
@@ -996,10 +996,10 @@
       <c r="F14" t="n">
         <v>1069.24696813025</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
         <v>6.97470991159236</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
         <v>30.9032382510869</v>
       </c>
@@ -1037,10 +1037,10 @@
       <c r="F15" t="n">
         <v>1086.50605251513</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
         <v>6.990722370334562</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
         <v>31.1367192409548</v>
       </c>
@@ -1079,10 +1079,10 @@
         <v>1155.10163274172</v>
       </c>
       <c r="G16" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="H16" t="n">
         <v>7.051943612800449</v>
-      </c>
-      <c r="H16" t="n">
-        <v>27.8</v>
       </c>
       <c r="I16" t="n">
         <v>31.1213721116744</v>
@@ -1121,10 +1121,10 @@
       <c r="F17" t="n">
         <v>1235.15939133951</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
         <v>7.118955302547687</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
         <v>30.7250782285817</v>
       </c>
@@ -1163,10 +1163,10 @@
         <v>1281.61054354933</v>
       </c>
       <c r="G18" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="H18" t="n">
         <v>7.155872803144588</v>
-      </c>
-      <c r="H18" t="n">
-        <v>28.8</v>
       </c>
       <c r="I18" t="n">
         <v>30.1616797630407</v>
@@ -1205,10 +1205,10 @@
       <c r="F19" t="n">
         <v>1333.09626557668</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
         <v>7.195259534807989</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
         <v>29.3985276965289</v>
       </c>
@@ -1246,10 +1246,10 @@
       <c r="F20" t="n">
         <v>1399.4537980287</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
         <v>7.243837295212061</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
         <v>28.4048995600246</v>
       </c>
@@ -1287,10 +1287,10 @@
       <c r="F21" t="n">
         <v>1484.31640682913</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
         <v>7.302709613149855</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
         <v>27.6564012026443</v>
       </c>
@@ -1328,10 +1328,10 @@
       <c r="F22" t="n">
         <v>1583.99815907985</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
         <v>7.367707410176632</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
         <v>27.34739147794</v>
       </c>
@@ -1369,10 +1369,10 @@
       <c r="F23" t="n">
         <v>1694.46534973825</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
         <v>7.435122542173674</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
         <v>26.6189999399789</v>
       </c>
@@ -1410,10 +1410,10 @@
       <c r="F24" t="n">
         <v>1788.69770318446</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
         <v>7.489243093928637</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
         <v>26.5000166464804</v>
       </c>
@@ -1451,10 +1451,10 @@
       <c r="F25" t="n">
         <v>1883.35772705062</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
         <v>7.540811487804754</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
         <v>26.4120919013735</v>
       </c>
@@ -1492,10 +1492,10 @@
       <c r="F26" t="n">
         <v>1936.03067741067</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
         <v>7.568395113480953</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
         <v>24.5914753075066</v>
       </c>
@@ -1533,10 +1533,10 @@
       <c r="F27" t="n">
         <v>1806.50110583878</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
         <v>7.499147162731864</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
         <v>25.1229058078344</v>
       </c>
@@ -1574,10 +1574,10 @@
       <c r="F28" t="n">
         <v>1965.30943437506</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
         <v>7.583404984870203</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
         <v>26.466523606501</v>
       </c>
@@ -1616,10 +1616,10 @@
         <v>2098.2112447615</v>
       </c>
       <c r="G29" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="H29" t="n">
         <v>7.648840472524994</v>
-      </c>
-      <c r="H29" t="n">
-        <v>25.5</v>
       </c>
       <c r="I29" t="n">
         <v>25.3845195629461</v>
@@ -1658,10 +1658,10 @@
       <c r="F30" t="n">
         <v>2270.9051808027</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
         <v>7.727933789055444</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
         <v>25.302936496264</v>
       </c>
@@ -1699,10 +1699,10 @@
       <c r="F31" t="n">
         <v>2396.94999213544</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
         <v>7.781952371528162</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
         <v>24.6285041297852</v>
       </c>

--- a/XLSX_DATA/RAW_DATA/IND_raw_data.xlsx
+++ b/XLSX_DATA/RAW_DATA/IND_raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,21 @@
           <t>palma_ratio</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>va_score</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>cc_score</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ge_score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -525,6 +540,9 @@
       <c r="M2" t="n">
         <v>3.100395256916996</v>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -568,6 +586,9 @@
       <c r="M3" t="n">
         <v>3.100236779794791</v>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -611,6 +632,15 @@
       <c r="M4" t="n">
         <v>3.046948356807512</v>
       </c>
+      <c r="N4" t="n">
+        <v>62.34</v>
+      </c>
+      <c r="O4" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>46.58</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -654,6 +684,9 @@
       <c r="M5" t="n">
         <v>3.144778481012658</v>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -695,6 +728,15 @@
       <c r="M6" t="n">
         <v>3.204617834394905</v>
       </c>
+      <c r="N6" t="n">
+        <v>62.35</v>
+      </c>
+      <c r="O6" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="P6" t="n">
+        <v>42.62</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -738,6 +780,9 @@
       <c r="M7" t="n">
         <v>3.236421725239616</v>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -781,6 +826,15 @@
       <c r="M8" t="n">
         <v>3.285140562248996</v>
       </c>
+      <c r="N8" t="n">
+        <v>61.45</v>
+      </c>
+      <c r="O8" t="n">
+        <v>43.58</v>
+      </c>
+      <c r="P8" t="n">
+        <v>40.68</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -824,6 +878,9 @@
       <c r="M9" t="n">
         <v>3.447454844006568</v>
       </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -867,6 +924,15 @@
       <c r="M10" t="n">
         <v>3.618807724601175</v>
       </c>
+      <c r="N10" t="n">
+        <v>62.35</v>
+      </c>
+      <c r="O10" t="n">
+        <v>36.59</v>
+      </c>
+      <c r="P10" t="n">
+        <v>41.97</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -910,6 +976,15 @@
       <c r="M11" t="n">
         <v>3.799828178694158</v>
       </c>
+      <c r="N11" t="n">
+        <v>62.67</v>
+      </c>
+      <c r="O11" t="n">
+        <v>36.77</v>
+      </c>
+      <c r="P11" t="n">
+        <v>43.03</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -953,6 +1028,15 @@
       <c r="M12" t="n">
         <v>3.994718309859155</v>
       </c>
+      <c r="N12" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>40</v>
+      </c>
+      <c r="P12" t="n">
+        <v>47.54</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -996,6 +1080,15 @@
       <c r="M13" t="n">
         <v>4.201263537906137</v>
       </c>
+      <c r="N13" t="n">
+        <v>64.37</v>
+      </c>
+      <c r="O13" t="n">
+        <v>39.57</v>
+      </c>
+      <c r="P13" t="n">
+        <v>47.82</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1039,6 +1132,15 @@
       <c r="M14" t="n">
         <v>4.427777777777778</v>
       </c>
+      <c r="N14" t="n">
+        <v>66.48</v>
+      </c>
+      <c r="O14" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>48.89</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1082,6 +1184,15 @@
       <c r="M15" t="n">
         <v>4.674595623215985</v>
       </c>
+      <c r="N15" t="n">
+        <v>66.53</v>
+      </c>
+      <c r="O15" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="P15" t="n">
+        <v>51.03</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1125,6 +1236,15 @@
       <c r="M16" t="n">
         <v>4.942213516160628</v>
       </c>
+      <c r="N16" t="n">
+        <v>65.72</v>
+      </c>
+      <c r="O16" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="P16" t="n">
+        <v>48.32</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1168,6 +1288,15 @@
       <c r="M17" t="n">
         <v>5.224798387096774</v>
       </c>
+      <c r="N17" t="n">
+        <v>65</v>
+      </c>
+      <c r="O17" t="n">
+        <v>40.87</v>
+      </c>
+      <c r="P17" t="n">
+        <v>49.52</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1211,6 +1340,15 @@
       <c r="M18" t="n">
         <v>5.531185031185032</v>
       </c>
+      <c r="N18" t="n">
+        <v>63.77</v>
+      </c>
+      <c r="O18" t="n">
+        <v>40.53</v>
+      </c>
+      <c r="P18" t="n">
+        <v>49.12</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1254,6 +1392,15 @@
       <c r="M19" t="n">
         <v>5.990228013029316</v>
       </c>
+      <c r="N19" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="P19" t="n">
+        <v>49.93</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1297,6 +1444,15 @@
       <c r="M20" t="n">
         <v>6.198008849557523</v>
       </c>
+      <c r="N20" t="n">
+        <v>61.65</v>
+      </c>
+      <c r="O20" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="P20" t="n">
+        <v>49.61</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1340,6 +1496,15 @@
       <c r="M21" t="n">
         <v>6.259176863181313</v>
       </c>
+      <c r="N21" t="n">
+        <v>62.14</v>
+      </c>
+      <c r="O21" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="P21" t="n">
+        <v>50.2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1383,6 +1548,15 @@
       <c r="M22" t="n">
         <v>6.484676503972759</v>
       </c>
+      <c r="N22" t="n">
+        <v>61.48</v>
+      </c>
+      <c r="O22" t="n">
+        <v>39.48</v>
+      </c>
+      <c r="P22" t="n">
+        <v>51.08</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1426,6 +1600,15 @@
       <c r="M23" t="n">
         <v>6.632606199770379</v>
       </c>
+      <c r="N23" t="n">
+        <v>62.05</v>
+      </c>
+      <c r="O23" t="n">
+        <v>40.87</v>
+      </c>
+      <c r="P23" t="n">
+        <v>59.06</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1469,6 +1652,15 @@
       <c r="M24" t="n">
         <v>7.026097271648874</v>
       </c>
+      <c r="N24" t="n">
+        <v>62.18</v>
+      </c>
+      <c r="O24" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="P24" t="n">
+        <v>58.65</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1512,6 +1704,15 @@
       <c r="M25" t="n">
         <v>7.195913461538462</v>
       </c>
+      <c r="N25" t="n">
+        <v>61.32</v>
+      </c>
+      <c r="O25" t="n">
+        <v>43.31</v>
+      </c>
+      <c r="P25" t="n">
+        <v>58.2</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1555,6 +1756,15 @@
       <c r="M26" t="n">
         <v>6.820601851851852</v>
       </c>
+      <c r="N26" t="n">
+        <v>60.41</v>
+      </c>
+      <c r="O26" t="n">
+        <v>43.65</v>
+      </c>
+      <c r="P26" t="n">
+        <v>61.09</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1598,6 +1808,15 @@
       <c r="M27" t="n">
         <v>6.647791619479049</v>
       </c>
+      <c r="N27" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="O27" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="P27" t="n">
+        <v>61.17</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1641,6 +1860,15 @@
       <c r="M28" t="n">
         <v>6.225321888412017</v>
       </c>
+      <c r="N28" t="n">
+        <v>57.84</v>
+      </c>
+      <c r="O28" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="P28" t="n">
+        <v>58.13</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1684,6 +1912,15 @@
       <c r="M29" t="n">
         <v>6.277238403451995</v>
       </c>
+      <c r="N29" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="O29" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="P29" t="n">
+        <v>56.01</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1727,6 +1964,15 @@
       <c r="M30" t="n">
         <v>6.543333333333333</v>
       </c>
+      <c r="N30" t="n">
+        <v>55.13</v>
+      </c>
+      <c r="O30" t="n">
+        <v>41.93</v>
+      </c>
+      <c r="P30" t="n">
+        <v>57.94</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1770,6 +2016,15 @@
       <c r="M31" t="n">
         <v>6.543333333333333</v>
       </c>
+      <c r="N31" t="n">
+        <v>54.35</v>
+      </c>
+      <c r="O31" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="P31" t="n">
+        <v>59.56</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1812,6 +2067,15 @@
       </c>
       <c r="M32" t="n">
         <v>6.543333333333333</v>
+      </c>
+      <c r="N32" t="n">
+        <v>55.47</v>
+      </c>
+      <c r="O32" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="P32" t="n">
+        <v>59.21</v>
       </c>
     </row>
   </sheetData>
